--- a/RouteOptima_Config.xlsx
+++ b/RouteOptima_Config.xlsx
@@ -9,8 +9,8 @@
   <sheets>
     <sheet name="Store_Locations" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Vehicle_Config" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Company_Settings" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Delivery_Locations" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Delivery_Locations" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Company_Settings" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -57,14 +57,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E74C3C"/>
-        <bgColor rgb="00E74C3C"/>
+        <fgColor rgb="00F39C12"/>
+        <bgColor rgb="00F39C12"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F39C12"/>
-        <bgColor rgb="00F39C12"/>
+        <fgColor rgb="00E74C3C"/>
+        <bgColor rgb="00E74C3C"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,10 +91,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -460,41 +460,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Store_ID</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Store_Name</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>Address</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Longitude</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>Contact_Phone</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Is_Active</t>
         </is>
@@ -509,23 +499,13 @@
           <t>Main Store</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>123 Main Street, City</t>
-        </is>
+      <c r="C2" t="n">
+        <v>23.0225</v>
       </c>
       <c r="D2" t="n">
-        <v>23.0225</v>
-      </c>
-      <c r="E2" t="n">
         <v>72.5714</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>+91-9876543210</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -540,23 +520,13 @@
           <t>Branch Store</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>456 Oak Avenue, City</t>
-        </is>
+      <c r="C3" t="n">
+        <v>23.0325</v>
       </c>
       <c r="D3" t="n">
-        <v>23.0325</v>
-      </c>
-      <c r="E3" t="n">
         <v>72.5814</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>+91-9876543211</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -568,23 +538,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sanatan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Pipodara</t>
-        </is>
+          <t>Sanatan Shipments</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>19.054999</v>
       </c>
       <c r="D4" t="n">
-        <v>21.34829</v>
-      </c>
-      <c r="E4" t="n">
-        <v>72.95831800000001</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>72.8692035</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -594,230 +559,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sanatan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Pipodara</t>
-        </is>
+          <t>Sanatan Shipments</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>19.054999</v>
       </c>
       <c r="D5" t="n">
-        <v>21.34829</v>
-      </c>
-      <c r="E5" t="n">
-        <v>72.95831800000001</v>
-      </c>
-      <c r="G5" t="inlineStr">
+        <v>72.8692035</v>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Sanatan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Pipodara</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>21.34829</v>
-      </c>
-      <c r="E6" t="n">
-        <v>72.95831800000001</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>96532986523</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Sanatan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Pipodara</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>21.34829</v>
-      </c>
-      <c r="E7" t="n">
-        <v>72.95831800000001</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>96532986523</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Sanatan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Pipodara</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>21.34829</v>
-      </c>
-      <c r="E8" t="n">
-        <v>72.95831800000001</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>96532986523</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Sanatan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Pipodara</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>21.34829</v>
-      </c>
-      <c r="E9" t="n">
-        <v>72.95831800000001</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>96532986523</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Sanatan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Pipodara</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>21.34829</v>
-      </c>
-      <c r="E10" t="n">
-        <v>72.95831800000001</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>96532986523</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Sanatan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Pipodara</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>21.34829</v>
-      </c>
-      <c r="E11" t="n">
-        <v>72.95831800000001</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>96532986523</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Sanatan</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>21.3482898</v>
-      </c>
-      <c r="E12" t="n">
-        <v>72.9583181</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -832,48 +585,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Vehicle_ID</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Store_ID</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Vehicle_Type</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Capacity_Shipments</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Max_Radius_KM</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Max_Trip_Time_Minutes</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Is_Active</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>Store_ID</t>
         </is>
       </c>
     </row>
@@ -881,24 +634,27 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>3W</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>50</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>15</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>240</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -908,24 +664,27 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>4W-EV</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>25</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>8</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>20</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>300</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -935,121 +694,34 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>4W</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Unlimited</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>25</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Unlimited</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>480</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>3W</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E5" t="n">
-        <v>15</v>
-      </c>
-      <c r="F5" t="n">
-        <v>480</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>3W</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" t="n">
-        <v>15</v>
-      </c>
-      <c r="F6" t="n">
-        <v>480</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>3W</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D7" t="n">
-        <v>5</v>
-      </c>
-      <c r="E7" t="n">
-        <v>15</v>
-      </c>
-      <c r="F7" t="n">
-        <v>480</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1063,91 +735,184 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Setting_Name</t>
+          <t>Delivery_ID</t>
         </is>
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>Setting_Value</t>
+          <t>Store_ID</t>
         </is>
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Customer_Name</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Delivery_Timeslot</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Is_Active</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Company_Name</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Your Company Name</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1001</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Name of your company</t>
+          <t>John Doe</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>123 Main St</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>23.0325</v>
+      </c>
+      <c r="F2" t="n">
+        <v>72.5814</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>09:00-12:00</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Default_Store_ID</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A3" t="n">
+        <v>1002</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Default store for route planning</t>
+          <t>Jane Smith</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>456 Oak Ave</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>23.0225</v>
+      </c>
+      <c r="F3" t="n">
+        <v>72.59139999999999</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>09:00-12:00</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Working_Hours_Start</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
+      <c r="A4" t="n">
+        <v>1003</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Business start time</t>
+          <t>Bob Johnson</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>789 Pine Rd</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>23.0425</v>
+      </c>
+      <c r="F4" t="n">
+        <v>72.5714</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>12:00-15:00</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Working_Hours_End</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
+      <c r="A5" t="n">
+        <v>1004</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Business end time</t>
+          <t>Alice Brown</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>321 Elm St</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>23.0125</v>
+      </c>
+      <c r="F5" t="n">
+        <v>72.56140000000001</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15:00-18:00</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1162,218 +927,91 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Delivery_ID</t>
+          <t>Setting_Name</t>
         </is>
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>Store_ID</t>
+          <t>Setting_Value</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>Customer_Name</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>Address</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>Latitude</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>Longitude</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>Delivery_Timeslot</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>Is_Active</t>
+          <t>Description</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1001</v>
-      </c>
-      <c r="B2" t="n">
-        <v>11</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Company_Name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Your Company Name</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Rajesh Patel</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Near Sanatan Temple, Pipodara</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>21.35829</v>
-      </c>
-      <c r="F2" t="n">
-        <v>72.96831800000001</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>09:00-12:00</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Name of your company</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>1002</v>
-      </c>
-      <c r="B3" t="n">
-        <v>11</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Default_Store_ID</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Priya Shah</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Pipodara Main Road</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>21.33829</v>
-      </c>
-      <c r="F3" t="n">
-        <v>72.978318</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>09:00-12:00</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Default store for route planning</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>1003</v>
-      </c>
-      <c r="B4" t="n">
-        <v>11</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Working_Hours_Start</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amit Kumar</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Sanatan Society, Pipodara</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>21.36829</v>
-      </c>
-      <c r="F4" t="n">
-        <v>72.948318</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>12:00-15:00</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Business start time</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>1004</v>
-      </c>
-      <c r="B5" t="n">
-        <v>11</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Working_Hours_End</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Neha Sharma</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Near Pipodara Station</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>21.32829</v>
-      </c>
-      <c r="F5" t="n">
-        <v>72.93831800000001</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>15:00-18:00</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>1005</v>
-      </c>
-      <c r="B6" t="n">
-        <v>11</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Vikram Singh</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Pipodara Market Area</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>21.36329</v>
-      </c>
-      <c r="F6" t="n">
-        <v>72.97331800000001</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>18:00-21:00</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Business end time</t>
         </is>
       </c>
     </row>
